--- a/EXCEL/Exercise Files/Chapter02/02_03_LogarithmicScale.xlsx
+++ b/EXCEL/Exercise Files/Chapter02/02_03_LogarithmicScale.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5233A4-98DD-4556-B63B-427306AE0935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7446F2D-C454-498C-B20C-C4CBFE940A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1295,17 +1304,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.84375" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1321,7 +1330,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1329,7 +1338,7 @@
         <v>9760</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1337,7 +1346,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1345,7 +1354,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1353,7 +1362,7 @@
         <v>681000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
@@ -1361,13 +1370,21 @@
         <v>90210000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="B13">
+        <f>2^3</f>
+        <v>8</v>
+      </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <f>LOG(8,2)</f>
         <v>3</v>
       </c>
     </row>
